--- a/自考本科/个人学习笔记/Byvm815/考试课程安排表.xlsx
+++ b/自考本科/个人学习笔记/Byvm815/考试课程安排表.xlsx
@@ -115,7 +115,7 @@
 免考13013-高级语言程序设计</t>
   </si>
   <si>
-    <t xml:space="preserve">(华南理工大学)
+    <t xml:space="preserve">华南理工大学
 实践科目</t>
   </si>
   <si>
